--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127446451</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127446122</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127446653</v>
       </c>
       <c r="B4" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127446673</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127446451</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127446122</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127446653</v>
       </c>
       <c r="B4" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127446673</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127446653</v>
       </c>
       <c r="B4" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127446451</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127446122</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127446653</v>
       </c>
       <c r="B4" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127446673</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127446451</v>
       </c>
       <c r="B2" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127446122</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127446653</v>
       </c>
       <c r="B4" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127446673</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127446653</v>
       </c>
       <c r="B4" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127446653</v>
       </c>
       <c r="B4" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127446653</v>
       </c>
       <c r="B4" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127446451</v>
+        <v>127446122</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498701</v>
+        <v>498727</v>
       </c>
       <c r="R2" t="n">
-        <v>6845989</v>
+        <v>6846146</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,26 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127446122</v>
+        <v>127446673</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498727</v>
+        <v>498710</v>
       </c>
       <c r="R3" t="n">
-        <v>6846146</v>
+        <v>6845978</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127446653</v>
+        <v>127446451</v>
       </c>
       <c r="B4" t="n">
-        <v>97347</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498724</v>
+        <v>498701</v>
       </c>
       <c r="R4" t="n">
-        <v>6845981</v>
+        <v>6845989</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127446673</v>
+        <v>127446653</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498710</v>
+        <v>498724</v>
       </c>
       <c r="R5" t="n">
-        <v>6845978</v>
+        <v>6845981</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1060,6 +1060,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127446429</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hivikilen, Hivikilen, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498718</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6846038</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35739-2025 artfynd.xlsx
+++ b/artfynd/A 35739-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127446122</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127446673</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127446451</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127446653</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127446429</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>